--- a/Book2_meta_titles.xlsx
+++ b/Book2_meta_titles.xlsx
@@ -695,26 +695,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>AGU75049015</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Upper Plate Assembly - AGU75049015 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>lgparts.com listing: upper plate assembly; fitment not stated (3rd pass); sheet brand "GE" differs from part-number brand "LG"</t>
         </is>
       </c>
     </row>
@@ -869,50 +875,62 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>WB27X21183</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>GE Range Control Panel Assembly - WB27X21183 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>HD Supply exact-number listing: control panel assembly for range (3rd pass); sheet brand "Samsung" differs from part-number brand "GE"</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>WB27X21183</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>GE Range Control Panel Assembly - WB27X21183 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>HD Supply exact-number listing: control panel assembly for range (3rd pass); sheet brand "Samsung" differs from part-number brand "GE"</t>
         </is>
       </c>
     </row>
@@ -2105,26 +2123,32 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>DE96-01027B</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Range Touch Control Panel - DE96-01027B | OEM Part</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>samsungparts.com listing: range touch control panel (sibling suffixes list other appliance types) (3rd pass)</t>
         </is>
       </c>
     </row>
@@ -2207,50 +2231,62 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>AGM30025504</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Control Panel - AGM30025504 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>lgparts.com listing: range control panel (3rd pass); sheet brand "Samsung" differs from part-number brand "LG"</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>DG47-00048C</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Oven Steam Heater - DG47-00048C | OEM Part</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>HnK Parts listing: steam heater for Samsung microwave oven (3rd pass)</t>
         </is>
       </c>
     </row>
@@ -4359,16 +4395,22 @@
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01193A | OEM Part</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>60</v>
+      </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+          <t>samsungparts.com listing: assembly drawer main module; appliance type not stated (3rd pass)</t>
         </is>
       </c>
     </row>
@@ -6347,26 +6389,32 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+      <c r="A222" s="3" t="inlineStr">
         <is>
           <t>DG94-01301G</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B222" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n"/>
-      <c r="D222" s="2" t="n"/>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Samsung Range Main Top - DG94-01301G | OEM Part</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>samsungparts.com range and oven collection lists it as Range Main Top (3rd pass); sheet brand "Bertazzoni" differs from part-number brand "Samsung"</t>
         </is>
       </c>
     </row>
@@ -8739,16 +8787,22 @@
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C314" s="2" t="n"/>
-      <c r="D314" s="2" t="n"/>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Frigidaire Clock/Timer - 318185731 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>45</v>
+      </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+          <t>Third-party reseller listings only (two mirror sites); appliance type not stated (3rd pass); sheet brand "GE" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -8831,50 +8885,62 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="inlineStr">
+      <c r="A318" s="3" t="inlineStr">
         <is>
           <t>316630003</t>
         </is>
       </c>
-      <c r="B318" s="2" t="inlineStr">
+      <c r="B318" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C318" s="2" t="n"/>
-      <c r="D318" s="2" t="n"/>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F318" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Wall Oven Electronic Controller - 316630003</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>iFixit listing: genuine Frigidaire wall oven electronic controller (3rd pass); sheet brand "GE" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="inlineStr">
+      <c r="A319" s="3" t="inlineStr">
         <is>
           <t>316630005</t>
         </is>
       </c>
-      <c r="B319" s="2" t="inlineStr">
+      <c r="B319" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C319" s="2" t="n"/>
-      <c r="D319" s="2" t="n"/>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F319" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Wall Oven Gas Electronic Controller - 316630005</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>iFixit listing title: Frigidaire free-standing wall oven gas electronic controller (3rd pass); sheet brand "Electrolux" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -9161,26 +9227,32 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="inlineStr">
+      <c r="A331" s="3" t="inlineStr">
         <is>
           <t>316282991</t>
         </is>
       </c>
-      <c r="B331" s="2" t="inlineStr">
+      <c r="B331" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n"/>
-      <c r="D331" s="2" t="n"/>
-      <c r="E331" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F331" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Maintop Assembly - 316282991 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F331" s="3" t="inlineStr">
+        <is>
+          <t>ereplacementparts listing: maintop assembly for Kenmore/Frigidaire electric ranges (3rd pass)</t>
         </is>
       </c>
     </row>
@@ -9233,26 +9305,32 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="inlineStr">
+      <c r="A334" s="3" t="inlineStr">
         <is>
           <t>5304513155</t>
         </is>
       </c>
-      <c r="B334" s="2" t="inlineStr">
+      <c r="B334" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n"/>
-      <c r="D334" s="2" t="n"/>
-      <c r="E334" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F334" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Smoothtop Assembly (Black) - 5304513155</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>Walmart listing: SMOOTHTOP,ASSEMBLY,BLACK (3rd pass); sheet brand "LG" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -12383,26 +12461,32 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="inlineStr">
+      <c r="A458" s="3" t="inlineStr">
         <is>
           <t>316630005</t>
         </is>
       </c>
-      <c r="B458" s="2" t="inlineStr">
+      <c r="B458" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C458" s="2" t="n"/>
-      <c r="D458" s="2" t="n"/>
-      <c r="E458" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F458" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Wall Oven Gas Electronic Controller - 316630005</t>
+        </is>
+      </c>
+      <c r="D458" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E458" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F458" s="3" t="inlineStr">
+        <is>
+          <t>iFixit listing title: Frigidaire free-standing wall oven gas electronic controller (3rd pass); sheet brand "Electrolux" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -12485,26 +12569,32 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="inlineStr">
+      <c r="A462" s="3" t="inlineStr">
         <is>
           <t>316630003</t>
         </is>
       </c>
-      <c r="B462" s="2" t="inlineStr">
+      <c r="B462" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C462" s="2" t="n"/>
-      <c r="D462" s="2" t="n"/>
-      <c r="E462" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F462" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Wall Oven Electronic Controller - 316630003</t>
+        </is>
+      </c>
+      <c r="D462" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="E462" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F462" s="3" t="inlineStr">
+        <is>
+          <t>iFixit listing: genuine Frigidaire wall oven electronic controller (3rd pass); sheet brand "GE" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -12543,16 +12633,22 @@
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C464" s="2" t="n"/>
-      <c r="D464" s="2" t="n"/>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>Frigidaire Clock/Timer - 318185731 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="n">
+        <v>45</v>
+      </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+          <t>Third-party reseller listings only (two mirror sites); appliance type not stated (3rd pass); sheet brand "GE" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -12785,26 +12881,32 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="inlineStr">
+      <c r="A474" s="3" t="inlineStr">
         <is>
           <t>5304513155</t>
         </is>
       </c>
-      <c r="B474" s="2" t="inlineStr">
+      <c r="B474" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C474" s="2" t="n"/>
-      <c r="D474" s="2" t="n"/>
-      <c r="E474" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F474" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Smoothtop Assembly (Black) - 5304513155</t>
+        </is>
+      </c>
+      <c r="D474" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F474" s="3" t="inlineStr">
+        <is>
+          <t>Walmart listing: SMOOTHTOP,ASSEMBLY,BLACK (3rd pass); sheet brand "LG" differs from part-number brand "Frigidaire"</t>
         </is>
       </c>
     </row>
@@ -13007,26 +13109,32 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="inlineStr">
+      <c r="A483" s="3" t="inlineStr">
         <is>
           <t>316282991</t>
         </is>
       </c>
-      <c r="B483" s="2" t="inlineStr">
+      <c r="B483" s="3" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C483" s="2" t="n"/>
-      <c r="D483" s="2" t="n"/>
-      <c r="E483" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F483" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Maintop Assembly - 316282991 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D483" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>ereplacementparts listing: maintop assembly for Kenmore/Frigidaire electric ranges (3rd pass)</t>
         </is>
       </c>
     </row>

--- a/Book2_meta_titles.xlsx
+++ b/Book2_meta_titles.xlsx
@@ -8027,26 +8027,32 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+      <c r="A286" s="3" t="inlineStr">
         <is>
           <t>11020735</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
+      <c r="B286" s="3" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C286" s="2" t="n"/>
-      <c r="D286" s="2" t="n"/>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>Needs review</t>
-        </is>
-      </c>
-      <c r="F286" s="2" t="inlineStr">
-        <is>
-          <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Bosch Wall Oven Control Board - 11020735 | OEM Part</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>Sears PartsDirect exact-number listing: wall oven control board (replaces 00758196, 12006840); brand taken from sheet (4th pass)</t>
         </is>
       </c>
     </row>

--- a/Book2_meta_titles.xlsx
+++ b/Book2_meta_titles.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -59,11 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F500"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -438,6 +444,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +478,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Generic fallback title (unverified part type)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -495,6 +507,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>GE Replacement Part - WB27X20745 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -519,6 +536,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>GE Replacement Part - WB27X20745 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -633,6 +655,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WP71001872 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -957,6 +984,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10780927 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -981,6 +1013,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Fisher &amp; Paykel Replacement Part - 211840P | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1005,6 +1042,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Fisher &amp; Paykel Replacement Part - 211840P | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1059,6 +1101,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10206087 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1083,6 +1130,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10877558 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1107,6 +1159,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03575A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1221,6 +1278,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11122533 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1275,6 +1337,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10734609 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1299,6 +1366,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10894095 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1323,6 +1395,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10177195 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1437,6 +1514,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11099813 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1461,6 +1543,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11088878 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1665,6 +1752,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - AGM75549801 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1719,6 +1811,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10904901 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1773,6 +1870,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE92-03967A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1797,6 +1899,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG96-00427A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1821,6 +1928,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE96-01050B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1875,6 +1987,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01281B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1899,6 +2016,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10453983 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1953,6 +2075,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10572538 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -2007,6 +2134,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10636386 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2091,6 +2223,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - AGU74969001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2205,6 +2342,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10196405BU | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2229,6 +2371,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - MEB63654001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2313,6 +2460,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG67-00166A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2337,6 +2489,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01961A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2361,6 +2518,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG67-00152A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2385,6 +2547,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01994A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2409,6 +2576,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG82-01521A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2433,6 +2605,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG82-01523A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2457,6 +2634,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG81-04117A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2481,6 +2663,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04247B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2505,6 +2692,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03701A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2559,6 +2751,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01141E | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2613,6 +2810,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01727C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2637,6 +2839,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG96-00728A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2691,6 +2898,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-02881D | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2745,6 +2957,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03551K | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2769,6 +2986,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG96-00773L | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2793,6 +3015,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG90-01358D | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2877,6 +3104,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03552C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2931,6 +3163,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-02896A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2955,6 +3192,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG90-01193C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2979,6 +3221,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG90-01232B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3003,6 +3250,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04664L | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3057,6 +3309,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG90-01184C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3111,6 +3368,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04664B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -3165,6 +3427,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-05016A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3189,6 +3456,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-02881C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3213,6 +3485,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03551D | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3237,6 +3514,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE81-04440A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3261,6 +3543,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04664H | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3285,6 +3572,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03952T | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3309,6 +3601,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG90-01232A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3333,6 +3630,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04148C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3447,6 +3749,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE81-04441A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3471,6 +3778,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE81-03806A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3615,6 +3927,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - AHB73129211 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3639,6 +3956,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - AGU75049016 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3663,6 +3985,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG98-01358A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3687,6 +4014,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE81-06920A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3711,6 +4043,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11297273 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3735,6 +4072,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10908095 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3759,6 +4101,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11091927 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3783,6 +4130,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10804319 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -3867,6 +4219,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10877560 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3891,6 +4248,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10872562 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3915,6 +4277,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10336325 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3939,6 +4306,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04293A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3993,6 +4365,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03584A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4017,6 +4394,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03580B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -4131,6 +4513,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-00513A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -4305,6 +4692,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04108B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -4359,6 +4751,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01301C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4383,6 +4780,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG96-00528A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4437,6 +4839,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03551C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4461,6 +4868,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03551A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4515,6 +4927,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03552K | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -4569,6 +4986,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03598B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -4593,6 +5015,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE94-05320A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -4707,6 +5134,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-05016D | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4731,6 +5163,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-02672A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -4785,6 +5222,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03549N | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4809,6 +5251,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03952W | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4833,6 +5280,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03952P | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -4857,6 +5309,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03577D | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4881,6 +5338,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE94-05062B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4905,6 +5367,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03580A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -4959,6 +5426,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01727E | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4983,6 +5455,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-03982A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -5007,6 +5484,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE94-05062C | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5031,6 +5513,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG90-01184A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5055,6 +5542,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04089A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5079,6 +5571,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10254671 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5103,6 +5600,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10472038 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5127,6 +5629,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10340694 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -5181,6 +5688,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10550508 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5385,6 +5897,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10314422 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5409,6 +5926,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W10314419 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -5493,6 +6015,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WPW10271737 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -5607,6 +6134,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WP8507P226-60 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5631,6 +6163,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE92-02439F | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -5715,6 +6252,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - MEE62306301 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -5949,6 +6491,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04148E | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6003,6 +6550,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DE81-04526A | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -6087,6 +6639,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11295990 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -6111,6 +6668,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - EBR87050404 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -6135,6 +6697,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - EBR87050401 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -6159,6 +6726,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - EBR85707901 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6213,6 +6785,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01301E | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -6357,6 +6934,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - W11122531 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -6441,6 +7023,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG92-01198F | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -6465,6 +7052,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01548B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -6489,6 +7081,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-01545B | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6543,6 +7140,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Replacement Part - DG94-04664P | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -6567,6 +7169,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - Z350251 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -6651,6 +7258,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 409047 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -6675,6 +7287,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125320 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -6729,6 +7346,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125190 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -6753,6 +7375,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125158 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -6777,6 +7404,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128006-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -6801,6 +7433,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1080923-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -6825,6 +7462,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1080921-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -6849,6 +7491,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128017-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -6873,6 +7520,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128023-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -6897,6 +7549,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128032-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -6921,6 +7578,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 200560 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -6945,6 +7607,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128019 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -6969,6 +7636,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 200558 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -7023,6 +7695,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - Z180301 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -7047,6 +7724,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125194 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -7101,6 +7783,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1081047 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -7125,6 +7812,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1081068 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -7149,6 +7841,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 11036753 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -7173,6 +7870,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 11031383 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -7197,6 +7899,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 681176 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -7221,6 +7928,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 267600065 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -7245,6 +7957,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600165 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -7269,6 +7986,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 771361 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -7323,6 +8045,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 716392 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -7377,6 +8104,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12026566 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -7431,6 +8163,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 626726 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -7455,6 +8192,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 683860 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -7479,6 +8221,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 449489 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -7503,6 +8250,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 318261301 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -7527,6 +8279,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 808751511 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -7551,6 +8308,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304508977 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -7605,6 +8367,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 676872 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -7629,6 +8396,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304495522 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -7653,6 +8425,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304495521 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -7797,6 +8574,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304503761 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -7851,6 +8633,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 649265 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -7875,6 +8662,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 709785 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -7899,6 +8691,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 618624 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -7923,6 +8720,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12012946 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -7947,6 +8749,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G282" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304511178 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -7971,6 +8778,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12011384 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -8025,6 +8837,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G285" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 709786 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -8079,6 +8896,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 11020740 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -8103,6 +8925,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 11020743 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -8127,6 +8954,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G289" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 798846 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -8151,6 +8983,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G290" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316472803 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -8295,6 +9132,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G295" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12028039 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -8319,6 +9161,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G296" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12009513 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -8343,6 +9190,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G297" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304524907 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -8397,6 +9249,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G299" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12035575 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -8421,6 +9278,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G300" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12035570 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -8535,6 +9397,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G304" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316418501 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -8559,6 +9426,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G305" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 318258201 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -8583,6 +9455,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316456238 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -8607,6 +9484,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G307" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 318022001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -8751,6 +9633,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G312" s="4" t="inlineStr">
+        <is>
+          <t>GE Replacement Part - WB57K10128 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -8865,6 +9752,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316531960 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -8889,6 +9781,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G317" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316650003 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
@@ -8973,6 +9870,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G320" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316462865 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -8997,6 +9899,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316462890 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -9021,6 +9928,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316453036 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -9045,6 +9957,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G323" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316531983 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -9129,6 +10046,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G326" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316462878 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -9183,6 +10105,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316630001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -9207,6 +10134,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G329" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316650001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -9231,6 +10163,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316630004 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -9285,6 +10222,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G332" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316442118 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -9309,6 +10251,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G333" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304514991 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -9363,6 +10310,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G335" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304513222 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -9387,6 +10339,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304514197 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -9411,6 +10368,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>GE Replacement Part - WB48X23580 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -9615,6 +10577,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304513242 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -9639,6 +10606,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304515481 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -9663,6 +10635,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 4410600043 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -9717,6 +10694,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304522786 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -9771,6 +10753,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304519397 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -9795,6 +10782,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G351" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304513844 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -9849,6 +10841,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G353" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600164 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -9903,6 +10900,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G355" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 669416 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -9927,6 +10929,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G356" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 20001930 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -9951,6 +10958,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G357" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 749003 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
@@ -10005,6 +11017,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 4410600082 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -10089,6 +11106,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G362" s="4" t="inlineStr">
+        <is>
+          <t>Whirlpool Replacement Part - WP6610457 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -10113,6 +11135,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 772646 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -10137,6 +11164,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G364" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 20004767 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -10161,6 +11193,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G365" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 10016262 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -10185,6 +11222,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G366" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 10016259 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -10209,6 +11251,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G367" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 11051367 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -10233,6 +11280,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G368" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 12046599 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -10257,6 +11309,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G369" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 23003198 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -10281,6 +11338,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G370" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 11019880 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -10305,6 +11367,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G371" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 681175 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -10329,6 +11396,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G372" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 703420 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -10353,6 +11425,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 710664 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -10377,6 +11454,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G374" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 771592 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -10401,6 +11483,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G375" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 771648 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -10425,6 +11512,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G376" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 774642 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -10479,6 +11571,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G378" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 20000020 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
@@ -10533,6 +11630,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 20000599 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -10557,6 +11659,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G381" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 673506 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -10581,6 +11688,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G382" s="4" t="inlineStr">
+        <is>
+          <t>Bosch Replacement Part - 659369 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -10605,6 +11717,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600498 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -10629,6 +11746,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 190264127 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -10653,6 +11775,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600551 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -10677,6 +11804,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G386" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 4410600086 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -10701,6 +11833,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G387" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600499 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -10725,6 +11862,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G388" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 260605048 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -10749,6 +11891,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G389" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 260605044 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -10773,6 +11920,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G390" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600217 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -10797,6 +11949,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G391" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 210600402 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -10821,6 +11978,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G392" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 267600066 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -10845,6 +12007,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>Blomberg Replacement Part - 267600080 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -10869,6 +12036,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G394" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128006 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -10893,6 +12065,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128023 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -10917,6 +12094,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G396" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128036 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -10941,6 +12123,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G397" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128021 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -10965,6 +12152,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G398" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128026 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -10989,6 +12181,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G399" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128003 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
@@ -11043,6 +12240,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G401" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128035 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -11067,6 +12269,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G402" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1081013 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -11091,6 +12298,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G403" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1081082 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -11115,6 +12327,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G404" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128010 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -11139,6 +12356,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128025 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
@@ -11193,6 +12415,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128036-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -11217,6 +12444,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G408" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128026-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -11271,6 +12503,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G410" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1081065 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -11295,6 +12532,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G411" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1080943-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -11319,6 +12561,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G412" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 128024-DA | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -11343,6 +12590,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G413" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 211258 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -11367,6 +12619,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G414" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - Z160143 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -11421,6 +12678,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G416" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125133 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -11445,6 +12707,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G417" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125153 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -11499,6 +12766,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G419" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125319 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -11523,6 +12795,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125335 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -11547,6 +12824,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G421" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125134 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -11571,6 +12853,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G422" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125345 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -11595,6 +12882,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G423" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125322 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -11649,6 +12941,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G425" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125170 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -11703,6 +13000,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125309 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -11727,6 +13029,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G428" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125321 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -11751,6 +13058,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125341 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -11775,6 +13087,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125346 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -11799,6 +13116,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G431" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 200536 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -11823,6 +13145,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G432" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125162 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -11847,6 +13174,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G433" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125187 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -11901,6 +13233,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G435" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125317 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -11925,6 +13262,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G436" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125323 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -11949,6 +13291,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G437" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125307 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -11973,6 +13320,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G438" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125318 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -11997,6 +13349,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 410701 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -12051,6 +13408,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G441" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 125339 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -12105,6 +13467,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G443" s="4" t="inlineStr">
+        <is>
+          <t>Bertazzoni Replacement Part - 1080442 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -12159,6 +13526,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G445" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316418501 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -12183,6 +13555,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316442118 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -12237,6 +13614,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G448" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316456238 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
@@ -12291,6 +13673,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G450" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316462890 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -12315,6 +13702,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G451" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316472803 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -12339,6 +13731,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G452" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316453036 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -12363,6 +13760,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G453" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316531983 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -12387,6 +13789,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316462865 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -12411,6 +13818,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316462878 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -12435,6 +13847,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316531960 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -12549,6 +13966,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G460" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316650001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -12573,6 +13995,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G461" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316630004 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
@@ -12627,6 +14054,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G463" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316630001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -12681,6 +14113,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G465" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 318022001 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -12705,6 +14142,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G466" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 318258201 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -12729,6 +14171,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G467" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 318261301 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -12783,6 +14230,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G469" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304495522 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -12807,6 +14259,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G470" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304503761 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -12831,6 +14288,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G471" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304508977 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -12855,6 +14317,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G472" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304511178 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -12939,6 +14406,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G475" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304513242 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -12963,6 +14435,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G476" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304513222 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -12987,6 +14464,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G477" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304514197 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -13011,6 +14493,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G478" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304514991 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -13035,6 +14522,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G479" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304519397 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -13059,6 +14551,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G480" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304524907 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -13113,6 +14610,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G482" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 808751511 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -13287,6 +14789,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G488" s="4" t="inlineStr">
+        <is>
+          <t>GE Replacement Part - WB56X25765 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -13311,6 +14818,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G489" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 316650003 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -13335,6 +14847,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G490" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304513844 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -13359,6 +14876,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G491" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304515481 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -13383,6 +14905,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G492" s="4" t="inlineStr">
+        <is>
+          <t>Frigidaire Replacement Part - 5304522786 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -13407,6 +14934,11 @@
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
         </is>
       </c>
+      <c r="G493" s="4" t="inlineStr">
+        <is>
+          <t>GE Replacement Part - WB27X43578 | OEM Part</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -13489,6 +15021,11 @@
       <c r="F496" s="2" t="inlineStr">
         <is>
           <t>No page found for this exact part number by web search; not confident enough to name the appliance/part</t>
+        </is>
+      </c>
+      <c r="G496" s="4" t="inlineStr">
+        <is>
+          <t>LG Replacement Part - MEB63654003 | OEM Part</t>
         </is>
       </c>
     </row>
